--- a/News_List.xlsx
+++ b/News_List.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\675939\Documents\PRIVATE\SensuCarens\website_sozai\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A20B802C-0299-4840-ACE3-B67D4AB4DDD3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43EA6BA-C55F-4166-B141-3293D36C81CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4760" yWindow="2900" windowWidth="14400" windowHeight="8170" xr2:uid="{56FC98A5-4C68-4567-8CC7-4556A897E792}"/>
+    <workbookView xWindow="2270" yWindow="1740" windowWidth="14400" windowHeight="8170" xr2:uid="{56FC98A5-4C68-4567-8CC7-4556A897E792}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -59,10 +59,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>Instagram を開設しました（@sensucarensofficial）</t>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>内容</t>
     <rPh sb="0" eb="2">
       <t>ナイヨウ</t>
@@ -89,13 +85,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>TikTikアカウントを開設しました</t>
-    <rPh sb="12" eb="14">
-      <t>カイセツ</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>Apr</t>
     <phoneticPr fontId="1"/>
   </si>
@@ -142,6 +131,17 @@
   </si>
   <si>
     <t>https://www.tiktok.com/@sensucarens</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Instagram アカウントを開設しました</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>TikTokアカウントを開設しました</t>
+    <rPh sb="12" eb="14">
+      <t>カイセツ</t>
+    </rPh>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -553,16 +553,16 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D1" t="s">
         <v>2</v>
       </c>
       <c r="E1" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -570,19 +570,19 @@
         <v>2024</v>
       </c>
       <c r="B2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C2">
         <v>11</v>
       </c>
       <c r="D2" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E2" t="s">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -590,19 +590,19 @@
         <v>2024</v>
       </c>
       <c r="B3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="C3">
         <v>12</v>
       </c>
       <c r="D3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>19</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -610,16 +610,16 @@
         <v>2025</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="C4">
         <v>12</v>
       </c>
       <c r="D4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E4" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -627,16 +627,16 @@
         <v>2025</v>
       </c>
       <c r="B5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="C5">
         <v>28</v>
       </c>
       <c r="D5" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="E5" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
@@ -644,16 +644,16 @@
         <v>2026</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="C6">
         <v>24</v>
       </c>
       <c r="D6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="E6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>

--- a/News_List.xlsx
+++ b/News_List.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10917"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\675939\Documents\PRIVATE\SensuCarens\website_sozai\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/chiaki/Documents/SensuCarens/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E43EA6BA-C55F-4166-B141-3293D36C81CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D78A6BB-95AC-7A49-92A1-5EABDA197860}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2270" yWindow="1740" windowWidth="14400" windowHeight="8170" xr2:uid="{56FC98A5-4C68-4567-8CC7-4556A897E792}"/>
+    <workbookView xWindow="2280" yWindow="1740" windowWidth="14400" windowHeight="8180" xr2:uid="{56FC98A5-4C68-4567-8CC7-4556A897E792}"/>
   </bookViews>
   <sheets>
     <sheet name="News" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="23">
   <si>
     <t>年</t>
     <rPh sb="0" eb="1">
@@ -142,6 +142,18 @@
     <rPh sb="12" eb="14">
       <t>カイセツ</t>
     </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>SEP</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>ALL</t>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>Websiteをリニューアルしました</t>
     <phoneticPr fontId="1"/>
   </si>
 </sst>
@@ -149,7 +161,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -542,10 +554,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB2B43FA-5F86-4962-9FC8-BDDB98E53AFE}">
-  <dimension ref="A1:F6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="18"/>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="1" spans="1:6">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -565,7 +577,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="2" spans="1:6">
       <c r="A2">
         <v>2024</v>
       </c>
@@ -585,7 +597,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="3" spans="1:6">
       <c r="A3">
         <v>2024</v>
       </c>
@@ -605,7 +617,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="4" spans="1:6">
       <c r="A4">
         <v>2025</v>
       </c>
@@ -622,7 +634,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="5" spans="1:6">
       <c r="A5">
         <v>2025</v>
       </c>
@@ -639,7 +651,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.55000000000000004">
+    <row r="6" spans="1:6">
       <c r="A6">
         <v>2026</v>
       </c>
@@ -654,6 +666,23 @@
       </c>
       <c r="E6" t="s">
         <v>12</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7">
+        <v>2026</v>
+      </c>
+      <c r="B7" t="s">
+        <v>20</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
